--- a/artfynd/S 897-2022 artfynd.xlsx
+++ b/artfynd/S 897-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136497596</v>
       </c>
       <c r="B2" t="n">
-        <v>98363</v>
+        <v>98366</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136497592</v>
       </c>
       <c r="B3" t="n">
-        <v>98421</v>
+        <v>98424</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136497594</v>
       </c>
       <c r="B4" t="n">
-        <v>98393</v>
+        <v>98396</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>136455467</v>
       </c>
       <c r="B5" t="n">
-        <v>99342</v>
+        <v>99345</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 897-2022 artfynd.xlsx
+++ b/artfynd/S 897-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136497596</v>
       </c>
       <c r="B2" t="n">
-        <v>98366</v>
+        <v>98367</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136497592</v>
       </c>
       <c r="B3" t="n">
-        <v>98424</v>
+        <v>98425</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136497594</v>
       </c>
       <c r="B4" t="n">
-        <v>98396</v>
+        <v>98397</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>136455467</v>
       </c>
       <c r="B5" t="n">
-        <v>99345</v>
+        <v>99346</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 897-2022 artfynd.xlsx
+++ b/artfynd/S 897-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136497596</v>
       </c>
       <c r="B2" t="n">
-        <v>98367</v>
+        <v>98372</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136497592</v>
       </c>
       <c r="B3" t="n">
-        <v>98425</v>
+        <v>98430</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136497594</v>
       </c>
       <c r="B4" t="n">
-        <v>98397</v>
+        <v>98402</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>136455467</v>
       </c>
       <c r="B5" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 897-2022 artfynd.xlsx
+++ b/artfynd/S 897-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136497596</v>
       </c>
       <c r="B2" t="n">
-        <v>98372</v>
+        <v>98374</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136497592</v>
       </c>
       <c r="B3" t="n">
-        <v>98430</v>
+        <v>98432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136497594</v>
       </c>
       <c r="B4" t="n">
-        <v>98402</v>
+        <v>98404</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>136455467</v>
       </c>
       <c r="B5" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 897-2022 artfynd.xlsx
+++ b/artfynd/S 897-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136497596</v>
       </c>
       <c r="B2" t="n">
-        <v>98374</v>
+        <v>98380</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136497592</v>
       </c>
       <c r="B3" t="n">
-        <v>98432</v>
+        <v>98438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136497594</v>
       </c>
       <c r="B4" t="n">
-        <v>98404</v>
+        <v>98410</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>136455467</v>
       </c>
       <c r="B5" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 897-2022 artfynd.xlsx
+++ b/artfynd/S 897-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136497596</v>
       </c>
       <c r="B2" t="n">
-        <v>98380</v>
+        <v>98382</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136497592</v>
       </c>
       <c r="B3" t="n">
-        <v>98438</v>
+        <v>98440</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136497594</v>
       </c>
       <c r="B4" t="n">
-        <v>98410</v>
+        <v>98412</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>136455467</v>
       </c>
       <c r="B5" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 897-2022 artfynd.xlsx
+++ b/artfynd/S 897-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136497596</v>
       </c>
       <c r="B2" t="n">
-        <v>98382</v>
+        <v>98383</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136497592</v>
       </c>
       <c r="B3" t="n">
-        <v>98440</v>
+        <v>98441</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136497594</v>
       </c>
       <c r="B4" t="n">
-        <v>98412</v>
+        <v>98413</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>136455467</v>
       </c>
       <c r="B5" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 897-2022 artfynd.xlsx
+++ b/artfynd/S 897-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136497596</v>
       </c>
       <c r="B2" t="n">
-        <v>98383</v>
+        <v>98389</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136497592</v>
       </c>
       <c r="B3" t="n">
-        <v>98441</v>
+        <v>98447</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136497594</v>
       </c>
       <c r="B4" t="n">
-        <v>98413</v>
+        <v>98419</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>136455467</v>
       </c>
       <c r="B5" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/S 897-2022 artfynd.xlsx
+++ b/artfynd/S 897-2022 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136497596</v>
       </c>
       <c r="B2" t="n">
-        <v>98389</v>
+        <v>98393</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>136497592</v>
       </c>
       <c r="B3" t="n">
-        <v>98447</v>
+        <v>98451</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>136497594</v>
       </c>
       <c r="B4" t="n">
-        <v>98419</v>
+        <v>98423</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
